--- a/results/reliability_eval/Llama-3-8B_P103_sample_30_tokens_0.1_temp_direct_query_scores_08-24-4.xlsx
+++ b/results/reliability_eval/Llama-3-8B_P103_sample_30_tokens_0.1_temp_direct_query_scores_08-24-4.xlsx
@@ -477,31 +477,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.430831180915406</v>
+        <v>0.4611774504243502</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7080891455101976</v>
+        <v>0.714018395869238</v>
       </c>
       <c r="C2" t="n">
-        <v>0.430831180915406</v>
+        <v>0.4611774504243502</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7080894911497013</v>
+        <v>0.714018395869238</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5710324654142536</v>
+        <v>0.5407079826887605</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7887788210503414</v>
+        <v>0.7542562828592199</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9905641206637468</v>
+        <v>0.9966251258232803</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9960130440863281</v>
+        <v>0.9984546852315513</v>
       </c>
       <c r="I2" t="n">
-        <v>0.751</v>
+        <v>0.733</v>
       </c>
     </row>
   </sheetData>
